--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A52755-621F-4A75-A4AB-A318B01555D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{13FACF68-87A9-442A-8EEC-FB2E7358B28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACD021D2-0AC7-4431-8F3A-6AAFC4BD0DDC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -195,13 +195,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,189 +489,15 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -690,6 +515,156 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1027,373 +1002,373 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" style="36" customWidth="1"/>
-    <col min="3" max="3" width="35.21875" style="46" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="57" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.54296875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="43" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" style="44" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" style="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="36.6" thickBot="1">
-      <c r="B1" s="28" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A2" s="61" t="s">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="24">
         <v>272</v>
       </c>
-      <c r="E2" s="49">
-        <v>220</v>
-      </c>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="30" t="s">
+      <c r="E2" s="25">
+        <v>217</v>
+      </c>
+      <c r="F2" s="26"/>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="27">
         <v>2</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="20">
         <v>1.3</v>
       </c>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="31" t="s">
+      <c r="F3" s="28"/>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="29">
         <v>1</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="30">
         <v>6</v>
       </c>
-      <c r="F4" s="15"/>
-    </row>
-    <row r="5" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A5" s="64" t="s">
+      <c r="F4" s="31"/>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="32">
         <v>150</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="33">
         <v>113</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="14">
         <f>67/113</f>
         <v>0.59292035398230092</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A6" s="65"/>
-      <c r="B6" s="33" t="s">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="34">
         <v>60</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="35">
         <v>103</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="16">
         <f>50/103</f>
         <v>0.4854368932038835</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A7" s="65"/>
-      <c r="B7" s="33" t="s">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="36">
         <v>12000</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="35">
         <v>12612</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="16">
         <v>0.43909999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="3" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A8" s="66"/>
-      <c r="B8" s="34" t="s">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="37">
         <v>150</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="38">
         <v>1444</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="18">
         <v>0.33650000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A9" s="61" t="s">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="39">
+        <v>6</v>
+      </c>
+      <c r="E9" s="40">
+        <v>15</v>
+      </c>
+      <c r="F9" s="26"/>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="47">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E10" s="49">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F10" s="28"/>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="46">
         <v>1</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E11" s="48">
+        <v>1</v>
+      </c>
+      <c r="F11" s="28"/>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="27">
+        <v>20</v>
+      </c>
+      <c r="E12" s="41">
+        <v>51</v>
+      </c>
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="29">
+        <v>30</v>
+      </c>
+      <c r="E13" s="30">
+        <v>23</v>
+      </c>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="27">
+        <v>30</v>
+      </c>
+      <c r="E14" s="41">
+        <v>140</v>
+      </c>
+      <c r="F14" s="42"/>
+    </row>
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="27">
+        <v>25</v>
+      </c>
+      <c r="E15" s="41">
+        <v>38</v>
+      </c>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="27">
+        <v>30</v>
+      </c>
+      <c r="E16" s="41">
+        <v>8</v>
+      </c>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="27">
+        <v>30</v>
+      </c>
+      <c r="E17" s="41">
+        <v>18</v>
+      </c>
+      <c r="F17" s="28"/>
+    </row>
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="29">
         <v>15</v>
       </c>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E10" s="47">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-      <c r="E11" s="56">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="2">
-        <v>20</v>
-      </c>
-      <c r="E12" s="56">
-        <v>51</v>
-      </c>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" s="3" customFormat="1" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="31" t="s">
+      <c r="E18" s="30">
         <v>30</v>
       </c>
-      <c r="C13" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="14">
-        <v>30</v>
-      </c>
-      <c r="E13" s="51">
-        <v>19</v>
-      </c>
-      <c r="F13" s="15"/>
-    </row>
-    <row r="14" spans="1:6" s="3" customFormat="1" ht="36" customHeight="1">
-      <c r="A14" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="11">
-        <v>30</v>
-      </c>
-      <c r="E14" s="55">
-        <v>38</v>
-      </c>
-      <c r="F14" s="24"/>
-    </row>
-    <row r="15" spans="1:6" s="3" customFormat="1" ht="12">
-      <c r="A15" s="62"/>
-      <c r="B15" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="2">
-        <v>30</v>
-      </c>
-      <c r="E15" s="56">
-        <v>83</v>
-      </c>
-      <c r="F15" s="25"/>
-    </row>
-    <row r="16" spans="1:6" s="3" customFormat="1" ht="24">
-      <c r="A16" s="62"/>
-      <c r="B16" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="2">
-        <v>30</v>
-      </c>
-      <c r="E16" s="56">
-        <v>8</v>
-      </c>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="24">
-      <c r="A17" s="62"/>
-      <c r="B17" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="2">
-        <v>30</v>
-      </c>
-      <c r="E17" s="56">
-        <v>18</v>
-      </c>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="36.6" thickBot="1">
-      <c r="A18" s="63"/>
-      <c r="B18" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="14">
-        <v>30</v>
-      </c>
-      <c r="E18" s="51">
-        <v>12</v>
-      </c>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="19" spans="1:6" s="3" customFormat="1" ht="30.6" customHeight="1">
-      <c r="A19" s="61" t="s">
+      <c r="F18" s="31"/>
+    </row>
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="54">
         <v>0.25</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="55">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="24">
-      <c r="A20" s="62"/>
-      <c r="B20" s="30" t="s">
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="56">
         <v>0.25</v>
       </c>
-      <c r="E20" s="59">
+      <c r="E20" s="48">
         <v>0.3611111111111111</v>
       </c>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="24.6" thickBot="1">
-      <c r="A21" s="63"/>
-      <c r="B21" s="31" t="s">
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" spans="1:6" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="57">
         <v>0.25</v>
       </c>
-      <c r="E21" s="60">
+      <c r="E21" s="58">
         <v>0.1111111111111111</v>
       </c>
-      <c r="F21" s="15"/>
+      <c r="F21" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1403,249 +1378,7 @@
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A14:A18"/>
   </mergeCells>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="formula" val="$D$2*50%"/>
-        <cfvo type="formula" val="$D$2*75%"/>
-        <cfvo type="formula" val="$D$2"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="formula" val="$D$3*50%"/>
-        <cfvo type="formula" val="$D$3*75%"/>
-        <cfvo type="formula" val="$D$3"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="formula" val="$D$4*50%"/>
-        <cfvo type="formula" val="$D$4*75%"/>
-        <cfvo type="formula" val="$D$4"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="formula" val="$D$5*50%"/>
-        <cfvo type="formula" val="$D$5*75%"/>
-        <cfvo type="formula" val="$D$5"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="formula" val="$D$6*50%"/>
-        <cfvo type="formula" val="$D$6*75%"/>
-        <cfvo type="formula" val="$D$6"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="formula" val="$D$6*50%"/>
-        <cfvo type="formula" val="$D$7*75%"/>
-        <cfvo type="formula" val="$D$7"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="$D$8*50%"/>
-        <cfvo type="formula" val="$D$8*75%"/>
-        <cfvo type="formula" val="$D$8"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$10"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="formula" val="$D$11*50%"/>
-        <cfvo type="formula" val="$D$11*75%"/>
-        <cfvo type="formula" val="$D$11"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="formula" val="$D$12*50%"/>
-        <cfvo type="formula" val="$D$12*75%"/>
-        <cfvo type="formula" val="$D$12"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$13*75%"/>
-        <cfvo type="formula" val="$D$13"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$14*75%"/>
-        <cfvo type="formula" val="$D$14"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="formula" val="$D$15*50%"/>
-        <cfvo type="formula" val="$D$15*75%"/>
-        <cfvo type="formula" val="$D$15"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="formula" val="$D$16*50%"/>
-        <cfvo type="formula" val="$D$16*75%"/>
-        <cfvo type="formula" val="$D$16"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="formula" val="$D$17*50%"/>
-        <cfvo type="formula" val="$D$17*75%"/>
-        <cfvo type="formula" val="$D$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="formula" val="$D$18*50%"/>
-        <cfvo type="formula" val="$D$18*75%"/>
-        <cfvo type="formula" val="$D$18"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="formula" val="$D$19*50%"/>
-        <cfvo type="formula" val="$D$19*75%"/>
-        <cfvo type="formula" val="$D$19"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="formula" val="$D$20*50%"/>
-        <cfvo type="formula" val="$D$20*75%"/>
-        <cfvo type="formula" val="$D$20"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="formula" val="$D$21*50%"/>
-        <cfvo type="formula" val="$D$21*75%"/>
-        <cfvo type="formula" val="$D$21"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40405010-A0C7-420C-A3B2-6E5CC8B2595A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04601E51-D4E5-40E9-9E5A-B76895A352FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Annual Target</t>
   </si>
@@ -107,9 +107,6 @@
     <t>KPI 7</t>
   </si>
   <si>
-    <t>Key Performance Indicator (KPI)</t>
-  </si>
-  <si>
     <t>Number of delivery partners trained</t>
   </si>
   <si>
@@ -198,6 +195,12 @@
   </si>
   <si>
     <t>KPI Metric</t>
+  </si>
+  <si>
+    <t>Key Performance Indicator (KPI) Pillar</t>
+  </si>
+  <si>
+    <t>KPI</t>
   </si>
 </sst>
 </file>
@@ -272,7 +275,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -480,19 +483,6 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -558,7 +548,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -657,25 +647,22 @@
     <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -684,22 +671,22 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1078,23 +1065,25 @@
     <col min="5" max="5" width="9.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="35" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="B1" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="36" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1106,12 +1095,12 @@
       <c r="D2" s="15">
         <v>272</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="37">
         <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="23" t="s">
         <v>16</v>
       </c>
@@ -1121,12 +1110,12 @@
       <c r="D3" s="17">
         <v>2</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="38">
         <v>1.7</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
@@ -1136,32 +1125,32 @@
       <c r="D4" s="18">
         <v>13</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="39">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="54" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="15">
         <v>150</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="40">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="27">
         <v>0.5</v>
@@ -1171,25 +1160,25 @@
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="56" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="19">
         <v>60</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="41">
         <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="56"/>
       <c r="C8" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="27">
         <v>0.5</v>
@@ -1199,25 +1188,25 @@
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57" t="s">
+      <c r="A9" s="52"/>
+      <c r="B9" s="56" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="20">
         <v>12000</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="41">
         <v>12612</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="27">
         <v>0.5</v>
@@ -1227,25 +1216,25 @@
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="57" t="s">
+      <c r="A11" s="52"/>
+      <c r="B11" s="56" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="20">
         <v>150</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="41">
         <v>1444</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="58"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" s="32">
         <v>0.5</v>
@@ -1255,56 +1244,56 @@
       </c>
     </row>
     <row r="13" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="48" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="16">
         <v>6</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="42">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="43">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>6</v>
@@ -1312,46 +1301,46 @@
       <c r="D16" s="17">
         <v>20</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="45">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="18">
         <v>30</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="39">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="48" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="15">
         <v>30</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="42">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
@@ -1359,61 +1348,61 @@
       <c r="D19" s="17">
         <v>25</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="45">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="17">
         <v>30</v>
       </c>
-      <c r="E20" s="46">
+      <c r="E20" s="45">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="45">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="18">
         <v>15</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="39">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="48" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
@@ -1421,14 +1410,14 @@
       <c r="D23" s="11">
         <v>0.25</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="46">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>11</v>
@@ -1436,14 +1425,14 @@
       <c r="D24" s="12">
         <v>0.25</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="44">
         <v>0.3611111111111111</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>12</v>
@@ -1451,21 +1440,21 @@
       <c r="D25" s="13">
         <v>0.25</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="47">
         <v>0.1111111111111111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A22"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04601E51-D4E5-40E9-9E5A-B76895A352FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD64363B-73B7-4E78-A918-9E80D4EE9524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Annual Target</t>
   </si>
@@ -201,6 +201,21 @@
   </si>
   <si>
     <t>KPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2027 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2028 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2029 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2030 Actual value </t>
   </si>
 </sst>
 </file>
@@ -548,7 +563,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -689,6 +704,18 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -707,17 +734,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1055,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="14" customWidth="1"/>
@@ -1065,7 +1083,7 @@
     <col min="5" max="5" width="9.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>52</v>
       </c>
@@ -1081,9 +1099,24 @@
       <c r="E1" s="36" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="F1" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1099,8 +1132,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
+    <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="53"/>
       <c r="B3" s="23" t="s">
         <v>16</v>
       </c>
@@ -1114,8 +1147,8 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50"/>
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="54"/>
       <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
@@ -1129,11 +1162,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="48" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1146,9 +1179,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="55"/>
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="56"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="26" t="s">
         <v>47</v>
       </c>
@@ -1159,9 +1192,9 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="56" t="s">
+    <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="56"/>
+      <c r="B7" s="50" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1174,9 +1207,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
-      <c r="B8" s="56"/>
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A8" s="56"/>
+      <c r="B8" s="50"/>
       <c r="C8" s="29" t="s">
         <v>45</v>
       </c>
@@ -1187,9 +1220,9 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
-      <c r="B9" s="56" t="s">
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="56"/>
+      <c r="B9" s="50" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1202,9 +1235,9 @@
         <v>12612</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
-      <c r="B10" s="56"/>
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="29" t="s">
         <v>23</v>
       </c>
@@ -1215,9 +1248,9 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
-      <c r="B11" s="56" t="s">
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="56"/>
+      <c r="B11" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1230,9 +1263,9 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="53"/>
-      <c r="B12" s="57"/>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="57"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="31" t="s">
         <v>50</v>
       </c>
@@ -1243,8 +1276,8 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="52" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="25" t="s">
@@ -1260,8 +1293,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="49"/>
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="53"/>
       <c r="B14" s="23" t="s">
         <v>33</v>
       </c>
@@ -1275,8 +1308,8 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="53"/>
       <c r="B15" s="23" t="s">
         <v>34</v>
       </c>
@@ -1290,8 +1323,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
+    <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="53"/>
       <c r="B16" s="23" t="s">
         <v>35</v>
       </c>
@@ -1306,7 +1339,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="24" t="s">
         <v>36</v>
       </c>
@@ -1321,7 +1354,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="52" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -1338,7 +1371,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="49"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="23" t="s">
         <v>38</v>
       </c>
@@ -1353,7 +1386,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="23" t="s">
         <v>39</v>
       </c>
@@ -1368,7 +1401,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="23" t="s">
         <v>40</v>
       </c>
@@ -1383,7 +1416,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="50"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="24" t="s">
         <v>41</v>
       </c>
@@ -1398,7 +1431,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="52" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="22" t="s">
@@ -1415,7 +1448,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="23" t="s">
         <v>43</v>
       </c>
@@ -1430,7 +1463,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="50"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="24" t="s">
         <v>44</v>
       </c>
@@ -1446,15 +1479,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD64363B-73B7-4E78-A918-9E80D4EE9524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5393BA-3E84-4F7E-9044-0EF4FB8478A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -222,10 +222,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -674,9 +675,6 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -704,6 +702,27 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -716,25 +735,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1099,24 +1100,24 @@
       <c r="E1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="47" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="48" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1133,22 +1134,22 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="17">
-        <v>2</v>
-      </c>
-      <c r="E3" s="38">
-        <v>1.7</v>
+      <c r="D3" s="58">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="58">
+        <v>1.5</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="54"/>
+      <c r="A4" s="50"/>
       <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
@@ -1158,15 +1159,15 @@
       <c r="D4" s="18">
         <v>13</v>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="38">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="54" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1175,13 +1176,13 @@
       <c r="D5" s="15">
         <v>150</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="39">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="56"/>
-      <c r="B6" s="49"/>
+      <c r="A6" s="52"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="26" t="s">
         <v>47</v>
       </c>
@@ -1193,8 +1194,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="56"/>
-      <c r="B7" s="50" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="56" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1203,13 +1204,13 @@
       <c r="D7" s="19">
         <v>60</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="40">
         <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="56"/>
-      <c r="B8" s="50"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="56"/>
       <c r="C8" s="29" t="s">
         <v>45</v>
       </c>
@@ -1221,8 +1222,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56"/>
-      <c r="B9" s="50" t="s">
+      <c r="A9" s="52"/>
+      <c r="B9" s="56" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1231,13 +1232,13 @@
       <c r="D9" s="20">
         <v>12000</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="40">
         <v>12612</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56"/>
-      <c r="B10" s="50"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="29" t="s">
         <v>23</v>
       </c>
@@ -1249,8 +1250,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="56"/>
-      <c r="B11" s="50" t="s">
+      <c r="A11" s="52"/>
+      <c r="B11" s="56" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1259,13 +1260,13 @@
       <c r="D11" s="20">
         <v>150</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="40">
         <v>1444</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="51"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="31" t="s">
         <v>50</v>
       </c>
@@ -1277,7 +1278,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="48" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="25" t="s">
@@ -1289,12 +1290,12 @@
       <c r="D13" s="16">
         <v>6</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="41">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="23" t="s">
         <v>33</v>
       </c>
@@ -1304,12 +1305,12 @@
       <c r="D14" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="42">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="53"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="23" t="s">
         <v>34</v>
       </c>
@@ -1319,12 +1320,12 @@
       <c r="D15" s="10">
         <v>1</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="43">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="53"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="23" t="s">
         <v>35</v>
       </c>
@@ -1334,12 +1335,12 @@
       <c r="D16" s="17">
         <v>20</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="44">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="24" t="s">
         <v>36</v>
       </c>
@@ -1349,12 +1350,12 @@
       <c r="D17" s="18">
         <v>30</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="38">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="48" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -1366,12 +1367,12 @@
       <c r="D18" s="15">
         <v>30</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="41">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="53"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="23" t="s">
         <v>38</v>
       </c>
@@ -1381,12 +1382,12 @@
       <c r="D19" s="17">
         <v>25</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="44">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="53"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="23" t="s">
         <v>39</v>
       </c>
@@ -1396,12 +1397,12 @@
       <c r="D20" s="17">
         <v>30</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="44">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="23" t="s">
         <v>40</v>
       </c>
@@ -1411,12 +1412,12 @@
       <c r="D21" s="17">
         <v>30</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="44">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="24" t="s">
         <v>41</v>
       </c>
@@ -1426,12 +1427,12 @@
       <c r="D22" s="18">
         <v>15</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="38">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="48" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="22" t="s">
@@ -1443,12 +1444,12 @@
       <c r="D23" s="11">
         <v>0.25</v>
       </c>
-      <c r="E23" s="46">
-        <v>0.41666666666666669</v>
+      <c r="E23" s="45">
+        <v>0.41660000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="23" t="s">
         <v>43</v>
       </c>
@@ -1458,12 +1459,12 @@
       <c r="D24" s="12">
         <v>0.25</v>
       </c>
-      <c r="E24" s="44">
-        <v>0.3611111111111111</v>
+      <c r="E24" s="43">
+        <v>0.36</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
+      <c r="A25" s="50"/>
       <c r="B25" s="24" t="s">
         <v>44</v>
       </c>
@@ -1473,12 +1474,13 @@
       <c r="D25" s="13">
         <v>0.25</v>
       </c>
-      <c r="E25" s="47">
-        <v>0.1111111111111111</v>
+      <c r="E25" s="46">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A17"/>
@@ -1487,7 +1489,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A23:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5393BA-3E84-4F7E-9044-0EF4FB8478A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6968D59-EBC4-4AED-9605-DD931C9AF111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -705,6 +705,9 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -734,9 +737,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1117,7 +1117,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1134,22 +1134,22 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
+      <c r="A3" s="50"/>
       <c r="B3" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="58">
-        <v>1.5</v>
-      </c>
-      <c r="E3" s="58">
-        <v>1.5</v>
+      <c r="D3" s="48">
+        <v>2</v>
+      </c>
+      <c r="E3" s="48">
+        <v>1.7</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50"/>
+      <c r="A4" s="51"/>
       <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
@@ -1164,10 +1164,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="55" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1181,8 +1181,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="55"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="26" t="s">
         <v>47</v>
       </c>
@@ -1194,8 +1194,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="56" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="57" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1209,8 +1209,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
-      <c r="B8" s="56"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="29" t="s">
         <v>45</v>
       </c>
@@ -1222,8 +1222,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
-      <c r="B9" s="56" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1237,8 +1237,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
-      <c r="B10" s="56"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="29" t="s">
         <v>23</v>
       </c>
@@ -1250,8 +1250,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
-      <c r="B11" s="56" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="57" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1265,8 +1265,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="53"/>
-      <c r="B12" s="57"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="31" t="s">
         <v>50</v>
       </c>
@@ -1278,7 +1278,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="49" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="25" t="s">
@@ -1295,7 +1295,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="49"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="23" t="s">
         <v>33</v>
       </c>
@@ -1310,7 +1310,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="23" t="s">
         <v>34</v>
       </c>
@@ -1325,7 +1325,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="49"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="23" t="s">
         <v>35</v>
       </c>
@@ -1340,7 +1340,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="24" t="s">
         <v>36</v>
       </c>
@@ -1355,7 +1355,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="49" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -1372,7 +1372,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="49"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="23" t="s">
         <v>38</v>
       </c>
@@ -1387,7 +1387,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="23" t="s">
         <v>39</v>
       </c>
@@ -1402,7 +1402,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="49"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="23" t="s">
         <v>40</v>
       </c>
@@ -1417,7 +1417,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="50"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="24" t="s">
         <v>41</v>
       </c>
@@ -1432,7 +1432,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="49" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="22" t="s">
@@ -1449,7 +1449,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="23" t="s">
         <v>43</v>
       </c>
@@ -1464,7 +1464,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="50"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="24" t="s">
         <v>44</v>
       </c>
@@ -1480,15 +1480,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A22"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6968D59-EBC4-4AED-9605-DD931C9AF111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="8_{13FACF68-87A9-442A-8EEC-FB2E7358B28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D76AFC2-8B74-457B-8181-12AD3B217C64}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Annual Target</t>
   </si>
@@ -107,6 +107,9 @@
     <t>KPI 7</t>
   </si>
   <si>
+    <t>Key Performance Indicator (KPI)</t>
+  </si>
+  <si>
     <t>Number of delivery partners trained</t>
   </si>
   <si>
@@ -195,27 +198,6 @@
   </si>
   <si>
     <t>KPI Metric</t>
-  </si>
-  <si>
-    <t>Key Performance Indicator (KPI) Pillar</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2027 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2028 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2029 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2030 Actual value </t>
   </si>
 </sst>
 </file>
@@ -223,10 +205,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -291,7 +273,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -507,6 +489,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -547,6 +542,127 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -561,10 +677,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -582,13 +698,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -606,25 +719,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -645,15 +758,9 @@
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -663,49 +770,46 @@
     <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -736,6 +840,51 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1074,407 +1223,390 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="21" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="36.26953125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <v>272</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="35">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="23" t="s">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="46"/>
+      <c r="B3" s="22" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="48">
+      <c r="D3" s="42">
         <v>2</v>
       </c>
-      <c r="E3" s="48">
+      <c r="E3" s="43">
         <v>1.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
-      <c r="B4" s="24" t="s">
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="47"/>
+      <c r="B4" s="23" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="44">
         <v>13</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="36">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="51" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="14">
+        <v>150</v>
+      </c>
+      <c r="E5" s="56">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="49"/>
+      <c r="B7" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="18">
+        <v>60</v>
+      </c>
+      <c r="E7" s="37">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A8" s="49"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D8" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="55">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="49"/>
+      <c r="B9" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="19">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="37">
+        <v>12612</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="49"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="55">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="49"/>
+      <c r="B11" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="19">
         <v>150</v>
       </c>
-      <c r="E5" s="39">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="27">
+      <c r="E11" s="37">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="50"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="29">
         <v>0.5</v>
       </c>
-      <c r="E6" s="28">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="19">
-        <v>60</v>
-      </c>
-      <c r="E7" s="40">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="30">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="20">
-        <v>12000</v>
-      </c>
-      <c r="E9" s="40">
-        <v>12612</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="27">
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="30">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="20">
-        <v>150</v>
-      </c>
-      <c r="E11" s="40">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="33">
+      <c r="E12" s="30">
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>30</v>
+      <c r="B13" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="16">
+        <v>25</v>
+      </c>
+      <c r="D13" s="15">
         <v>6</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="38">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
-      <c r="B14" s="23" t="s">
-        <v>33</v>
+    <row r="14" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46"/>
+      <c r="B14" s="22" t="s">
+        <v>34</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="9">
+        <v>26</v>
+      </c>
+      <c r="D14" s="8">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="39">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
-      <c r="B15" s="23" t="s">
-        <v>34</v>
+    <row r="15" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="46"/>
+      <c r="B15" s="22" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="10">
+        <v>27</v>
+      </c>
+      <c r="D15" s="9">
         <v>1</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="40">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-      <c r="B16" s="23" t="s">
-        <v>35</v>
+    <row r="16" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="46"/>
+      <c r="B16" s="22" t="s">
+        <v>36</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <v>20</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="41">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
-      <c r="B17" s="24" t="s">
-        <v>36</v>
+      <c r="A17" s="47"/>
+      <c r="B17" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="18">
+        <v>28</v>
+      </c>
+      <c r="D17" s="17">
         <v>30</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="36">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+    <row r="18" spans="1:5" s="2" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>37</v>
+      <c r="B18" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="15">
+        <v>29</v>
+      </c>
+      <c r="D18" s="14">
         <v>30</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="38">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="23" t="s">
-        <v>38</v>
+      <c r="A19" s="46"/>
+      <c r="B19" s="22" t="s">
+        <v>39</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <v>25</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="41">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
-      <c r="B20" s="23" t="s">
-        <v>39</v>
+      <c r="A20" s="46"/>
+      <c r="B20" s="22" t="s">
+        <v>40</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="17">
         <v>30</v>
       </c>
-      <c r="E20" s="44">
+      <c r="D20" s="16">
+        <v>30</v>
+      </c>
+      <c r="E20" s="41">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
-      <c r="B21" s="23" t="s">
-        <v>40</v>
+    <row r="21" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
+      <c r="A21" s="46"/>
+      <c r="B21" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="17">
+        <v>32</v>
+      </c>
+      <c r="D21" s="16">
         <v>30</v>
       </c>
-      <c r="E21" s="44">
+      <c r="E21" s="41">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="18">
+    <row r="22" spans="1:5" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="46"/>
+      <c r="B22" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="59">
         <v>15</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="60">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+    <row r="23" spans="1:5" s="2" customFormat="1" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>42</v>
+      <c r="B23" s="64" t="s">
+        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>0.25</v>
       </c>
-      <c r="E23" s="45">
-        <v>0.41660000000000003</v>
+      <c r="E23" s="61">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="23" t="s">
-        <v>43</v>
+      <c r="A24" s="68"/>
+      <c r="B24" s="65" t="s">
+        <v>44</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <v>0.25</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="62">
         <v>0.36</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
-      <c r="B25" s="24" t="s">
-        <v>44</v>
+    <row r="25" spans="1:5" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="69"/>
+      <c r="B25" s="66" t="s">
+        <v>45</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <v>0.25</v>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="63">
         <v>0.11</v>
       </c>
     </row>
@@ -1490,13 +1622,235 @@
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A22"/>
   </mergeCells>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="$D$2/2"/>
+        <cfvo type="formula" val="$D$2"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$3/2"/>
+        <cfvo type="formula" val="$D$3"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$4/2"/>
+        <cfvo type="formula" val="$D$4"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E6">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$6/2"/>
+        <cfvo type="formula" val="$D$6"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E8">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$8/2"/>
+        <cfvo type="formula" val="$D$8"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9:E10">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$10/2"/>
+        <cfvo type="formula" val="$D$10"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$11/2"/>
+        <cfvo type="formula" val="$D$11"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="$D$13/2"/>
+        <cfvo type="formula" val="$D$13"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$12/2"/>
+        <cfvo type="formula" val="$D$12"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$14/2"/>
+        <cfvo type="formula" val="$D$14"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="$D$15/2"/>
+        <cfvo type="formula" val="$D$15"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$16/2"/>
+        <cfvo type="formula" val="$D$16"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$17/2"/>
+        <cfvo type="formula" val="$D$17"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$18/2"/>
+        <cfvo type="formula" val="$D$18"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$19/2"/>
+        <cfvo type="formula" val="$D$19"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$20/2"/>
+        <cfvo type="formula" val="$D$20"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$21/2"/>
+        <cfvo type="formula" val="$D$21"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E22">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$22/2"/>
+        <cfvo type="formula" val="$D$22"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E25">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="formula" val="$D$24/2"/>
+        <cfvo type="formula" val="$D$24"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/s_lewis_cgiar_org/Documents/TAAT/R4D/KPIS/Alekeh/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="8_{13FACF68-87A9-442A-8EEC-FB2E7358B28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D76AFC2-8B74-457B-8181-12AD3B217C64}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6968D59-EBC4-4AED-9605-DD931C9AF111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Annual Target</t>
   </si>
@@ -107,9 +107,6 @@
     <t>KPI 7</t>
   </si>
   <si>
-    <t>Key Performance Indicator (KPI)</t>
-  </si>
-  <si>
     <t>Number of delivery partners trained</t>
   </si>
   <si>
@@ -198,6 +195,27 @@
   </si>
   <si>
     <t>KPI Metric</t>
+  </si>
+  <si>
+    <t>Key Performance Indicator (KPI) Pillar</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2027 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2028 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2029 Actual value </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2030 Actual value </t>
   </si>
 </sst>
 </file>
@@ -205,10 +223,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -273,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -489,19 +507,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -542,127 +547,6 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -677,10 +561,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -698,10 +582,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -719,25 +606,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -758,9 +645,15 @@
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -770,46 +663,49 @@
     <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -840,51 +736,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1223,390 +1074,407 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="36.26953125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6328125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="36.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="31"/>
-      <c r="B1" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="32" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="B1" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="36" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="F1" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="47" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="15">
         <v>272</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="37">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
-      <c r="B3" s="22" t="s">
+    <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50"/>
+      <c r="B3" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="48">
         <v>2</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="48">
         <v>1.7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47"/>
-      <c r="B4" s="23" t="s">
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="51"/>
+      <c r="B4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="18">
         <v>13</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="38">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="55" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="15">
+        <v>150</v>
+      </c>
+      <c r="E5" s="39">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="53"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D6" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="28">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="53"/>
+      <c r="B7" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="19">
+        <v>60</v>
+      </c>
+      <c r="E7" s="40">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A8" s="53"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="30">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="53"/>
+      <c r="B9" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="20">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="40">
+        <v>12612</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="53"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="30">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="53"/>
+      <c r="B11" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="20">
         <v>150</v>
       </c>
-      <c r="E5" s="56">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="26">
+      <c r="E11" s="40">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="54"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="32">
         <v>0.5</v>
       </c>
-      <c r="E6" s="11">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="2" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="18">
-        <v>60</v>
-      </c>
-      <c r="E7" s="37">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="55">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
-      <c r="B9" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="19">
-        <v>12000</v>
-      </c>
-      <c r="E9" s="37">
-        <v>12612</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="49"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="27" t="s">
+      <c r="E12" s="33">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="55">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49"/>
-      <c r="B11" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="19">
-        <v>150</v>
-      </c>
-      <c r="E11" s="37">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="50"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="16">
+        <v>6</v>
+      </c>
+      <c r="E13" s="41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="50"/>
+      <c r="B14" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="15">
-        <v>6</v>
-      </c>
-      <c r="E13" s="38">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
-      <c r="B14" s="22" t="s">
+      <c r="D14" s="9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E14" s="42">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50"/>
+      <c r="B15" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E14" s="39">
-        <v>1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
-      <c r="B15" s="22" t="s">
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="50"/>
+      <c r="B16" s="23" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="9">
-        <v>1</v>
-      </c>
-      <c r="E15" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="46"/>
-      <c r="B16" s="22" t="s">
-        <v>36</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>20</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="44">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="47"/>
-      <c r="B17" s="23" t="s">
+      <c r="A17" s="51"/>
+      <c r="B17" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="18">
+        <v>30</v>
+      </c>
+      <c r="E17" s="38">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D18" s="15">
         <v>30</v>
       </c>
-      <c r="E17" s="36">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="2" customFormat="1" ht="36.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="21" t="s">
+      <c r="E18" s="41">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="50"/>
+      <c r="B19" s="23" t="s">
         <v>38</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="14">
-        <v>30</v>
-      </c>
-      <c r="E18" s="38">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
-      <c r="B19" s="22" t="s">
-        <v>39</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="17">
         <v>25</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="44">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
-      <c r="B20" s="22" t="s">
+      <c r="A20" s="50"/>
+      <c r="B20" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="17">
+        <v>30</v>
+      </c>
+      <c r="E20" s="44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="50"/>
+      <c r="B21" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="17">
         <v>30</v>
       </c>
-      <c r="D20" s="16">
+      <c r="E21" s="44">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="51"/>
+      <c r="B22" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="18">
+        <v>15</v>
+      </c>
+      <c r="E22" s="38">
         <v>30</v>
       </c>
-      <c r="E20" s="41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
-      <c r="B21" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="16">
-        <v>30</v>
-      </c>
-      <c r="E21" s="41">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="57" t="s">
+    </row>
+    <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>42</v>
-      </c>
-      <c r="C22" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="59">
-        <v>15</v>
-      </c>
-      <c r="E22" s="60">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="2" customFormat="1" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="11">
         <v>0.25</v>
       </c>
-      <c r="E23" s="61">
-        <v>0.41666666666666669</v>
+      <c r="E23" s="45">
+        <v>0.41660000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="68"/>
-      <c r="B24" s="65" t="s">
-        <v>44</v>
+      <c r="A24" s="50"/>
+      <c r="B24" s="23" t="s">
+        <v>43</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="12">
         <v>0.25</v>
       </c>
-      <c r="E24" s="62">
+      <c r="E24" s="43">
         <v>0.36</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" ht="24.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="69"/>
-      <c r="B25" s="66" t="s">
-        <v>45</v>
+    <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="51"/>
+      <c r="B25" s="24" t="s">
+        <v>44</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="13">
         <v>0.25</v>
       </c>
-      <c r="E25" s="63">
+      <c r="E25" s="46">
         <v>0.11</v>
       </c>
     </row>
@@ -1622,235 +1490,13 @@
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A22"/>
   </mergeCells>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="$D$2/2"/>
-        <cfvo type="formula" val="$D$2"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$3/2"/>
-        <cfvo type="formula" val="$D$3"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$4/2"/>
-        <cfvo type="formula" val="$D$4"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$6/2"/>
-        <cfvo type="formula" val="$D$6"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E8">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$8/2"/>
-        <cfvo type="formula" val="$D$8"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E10">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$10/2"/>
-        <cfvo type="formula" val="$D$10"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$11/2"/>
-        <cfvo type="formula" val="$D$11"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E13">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="$D$13/2"/>
-        <cfvo type="formula" val="$D$13"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E12">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$12/2"/>
-        <cfvo type="formula" val="$D$12"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$14/2"/>
-        <cfvo type="formula" val="$D$14"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="$D$15/2"/>
-        <cfvo type="formula" val="$D$15"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$16/2"/>
-        <cfvo type="formula" val="$D$16"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$17/2"/>
-        <cfvo type="formula" val="$D$17"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$18/2"/>
-        <cfvo type="formula" val="$D$18"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$19/2"/>
-        <cfvo type="formula" val="$D$19"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$20/2"/>
-        <cfvo type="formula" val="$D$20"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$21/2"/>
-        <cfvo type="formula" val="$D$21"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E22">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$22/2"/>
-        <cfvo type="formula" val="$D$22"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:E25">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="formula" val="$D$24/2"/>
-        <cfvo type="formula" val="$D$24"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9d258917-277f-42cd-a3cd-14c4e9ee58bc}" enabled="1" method="Standard" siteId="{38ae3bcd-9579-4fd4-adda-b42e1495d55a}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6968D59-EBC4-4AED-9605-DD931C9AF111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8A0CDE-B9FF-4596-8D2D-45B72900FCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -39,14 +39,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Annual Target</t>
   </si>
   <si>
-    <t>2025 Actual value</t>
-  </si>
-  <si>
     <t>Research Outputs</t>
   </si>
   <si>
@@ -201,21 +198,6 @@
   </si>
   <si>
     <t>KPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2026 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2027 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2028 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2029 Actual value </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2030 Actual value </t>
   </si>
 </sst>
 </file>
@@ -669,9 +651,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -702,12 +681,21 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -726,17 +714,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1086,105 +1068,105 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>53</v>
-      </c>
       <c r="C1" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="57">
+        <v>2025</v>
+      </c>
+      <c r="F1" s="58">
+        <v>2026</v>
+      </c>
+      <c r="G1" s="58">
+        <v>2027</v>
+      </c>
+      <c r="H1" s="58">
+        <v>2028</v>
+      </c>
+      <c r="I1" s="58">
+        <v>2029</v>
+      </c>
+      <c r="J1" s="58">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="B2" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="D2" s="15">
         <v>272</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="36">
         <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
+      <c r="A3" s="52"/>
       <c r="B3" s="23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="48">
+        <v>12</v>
+      </c>
+      <c r="D3" s="46">
         <v>2</v>
       </c>
-      <c r="E3" s="48">
+      <c r="E3" s="46">
         <v>1.7</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
+      <c r="A4" s="53"/>
       <c r="B4" s="24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="18">
         <v>13</v>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="37">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>17</v>
+      <c r="A5" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="15">
         <v>150</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="38">
         <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="48"/>
       <c r="C6" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="27">
         <v>0.5</v>
@@ -1194,25 +1176,25 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57" t="s">
-        <v>19</v>
+      <c r="A7" s="55"/>
+      <c r="B7" s="49" t="s">
+        <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="19">
         <v>60</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="39">
         <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="27">
         <v>0.5</v>
@@ -1222,25 +1204,25 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57" t="s">
-        <v>20</v>
+      <c r="A9" s="55"/>
+      <c r="B9" s="49" t="s">
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="20">
         <v>12000</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="39">
         <v>12612</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="49"/>
       <c r="C10" s="29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="27">
         <v>0.5</v>
@@ -1250,25 +1232,25 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="57" t="s">
-        <v>21</v>
+      <c r="A11" s="55"/>
+      <c r="B11" s="49" t="s">
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="20">
         <v>150</v>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="39">
         <v>1444</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="58"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="50"/>
       <c r="C12" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="32">
         <v>0.5</v>
@@ -1278,217 +1260,217 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
-        <v>5</v>
+      <c r="A13" s="51" t="s">
+        <v>4</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="16">
         <v>6</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="40">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="41">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="42">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="17">
         <v>20</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="43">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="18">
         <v>30</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="37">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
-        <v>7</v>
+      <c r="A18" s="51" t="s">
+        <v>6</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="15">
         <v>30</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="40">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="17">
         <v>25</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="43">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="17">
         <v>30</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="43">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
       </c>
-      <c r="E21" s="44">
+      <c r="E21" s="43">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" s="18">
         <v>15</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="37">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="D23" s="11">
         <v>0.25</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="44">
         <v>0.41660000000000003</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="12">
         <v>0.25</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="42">
         <v>0.36</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="13">
         <v>0.25</v>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="45">
         <v>0.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8A0CDE-B9FF-4596-8D2D-45B72900FCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7DB386-D46E-4DE3-A8EC-1CAE7F89F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -684,6 +684,30 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -695,30 +719,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1079,27 +1079,27 @@
       <c r="D1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="57">
+      <c r="E1" s="47">
         <v>2025</v>
       </c>
-      <c r="F1" s="58">
+      <c r="F1" s="48">
         <v>2026</v>
       </c>
-      <c r="G1" s="58">
+      <c r="G1" s="48">
         <v>2027</v>
       </c>
-      <c r="H1" s="58">
+      <c r="H1" s="48">
         <v>2028</v>
       </c>
-      <c r="I1" s="58">
+      <c r="I1" s="48">
         <v>2029</v>
       </c>
-      <c r="J1" s="58">
+      <c r="J1" s="48">
         <v>2030</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1116,7 +1116,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
+      <c r="A3" s="50"/>
       <c r="B3" s="23" t="s">
         <v>15</v>
       </c>
@@ -1131,7 +1131,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53"/>
+      <c r="A4" s="51"/>
       <c r="B4" s="24" t="s">
         <v>14</v>
       </c>
@@ -1146,10 +1146,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="55" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1163,8 +1163,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="48"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="26" t="s">
         <v>46</v>
       </c>
@@ -1176,8 +1176,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
-      <c r="B7" s="49" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="57" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1191,8 +1191,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="49"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="29" t="s">
         <v>44</v>
       </c>
@@ -1204,8 +1204,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
-      <c r="B9" s="49" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="57" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1219,8 +1219,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
-      <c r="B10" s="49"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="29" t="s">
         <v>22</v>
       </c>
@@ -1232,8 +1232,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="49" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1247,8 +1247,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
-      <c r="B12" s="50"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="31" t="s">
         <v>49</v>
       </c>
@@ -1260,7 +1260,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="49" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="25" t="s">
@@ -1273,11 +1273,11 @@
         <v>6</v>
       </c>
       <c r="E13" s="40">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="23" t="s">
         <v>32</v>
       </c>
@@ -1292,7 +1292,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="23" t="s">
         <v>33</v>
       </c>
@@ -1307,7 +1307,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="23" t="s">
         <v>34</v>
       </c>
@@ -1322,7 +1322,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="53"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="24" t="s">
         <v>35</v>
       </c>
@@ -1337,7 +1337,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="49" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -1354,7 +1354,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="23" t="s">
         <v>37</v>
       </c>
@@ -1369,7 +1369,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="23" t="s">
         <v>38</v>
       </c>
@@ -1384,7 +1384,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="23" t="s">
         <v>39</v>
       </c>
@@ -1399,7 +1399,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="24" t="s">
         <v>40</v>
       </c>
@@ -1414,7 +1414,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="49" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="22" t="s">
@@ -1431,7 +1431,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="23" t="s">
         <v>42</v>
       </c>
@@ -1446,7 +1446,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="24" t="s">
         <v>43</v>
       </c>
@@ -1462,6 +1462,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A17"/>
@@ -1470,7 +1471,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A23:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7DB386-D46E-4DE3-A8EC-1CAE7F89F0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991B9B04-AB71-4EF7-9DB4-78C734AE5A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,9 +107,6 @@
     <t>Number of delivery partners trained</t>
   </si>
   <si>
-    <t>Number of delivery partners trained who are female</t>
-  </si>
-  <si>
     <t>Number of varieties released</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
     <t>Number of national scientists who attended training courses</t>
   </si>
   <si>
-    <t>Number of national scientists who attended training courses who are female</t>
-  </si>
-  <si>
     <t>KPI Metric</t>
   </si>
   <si>
@@ -198,6 +192,12 @@
   </si>
   <si>
     <t>KPI</t>
+  </si>
+  <si>
+    <t>Percentage of delivery partners trained who are female</t>
+  </si>
+  <si>
+    <t>Percentage of national scientists who attended training courses who are female</t>
   </si>
 </sst>
 </file>
@@ -1068,13 +1068,13 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="15">
         <v>150</v>
@@ -1166,7 +1166,7 @@
       <c r="A6" s="53"/>
       <c r="B6" s="56"/>
       <c r="C6" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="27">
         <v>0.5</v>
@@ -1181,7 +1181,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="19">
         <v>60</v>
@@ -1194,7 +1194,7 @@
       <c r="A8" s="53"/>
       <c r="B8" s="57"/>
       <c r="C8" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="27">
         <v>0.5</v>
@@ -1222,7 +1222,7 @@
       <c r="A10" s="53"/>
       <c r="B10" s="57"/>
       <c r="C10" s="29" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D10" s="27">
         <v>0.5</v>
@@ -1237,7 +1237,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" s="20">
         <v>150</v>
@@ -1250,7 +1250,7 @@
       <c r="A12" s="54"/>
       <c r="B12" s="58"/>
       <c r="C12" s="31" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="32">
         <v>0.5</v>
@@ -1264,10 +1264,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="16">
         <v>6</v>
@@ -1279,10 +1279,10 @@
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50"/>
       <c r="B14" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="9">
         <v>1.4999999999999999E-2</v>
@@ -1294,10 +1294,10 @@
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="50"/>
       <c r="B15" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
@@ -1309,7 +1309,7 @@
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50"/>
       <c r="B16" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>5</v>
@@ -1324,10 +1324,10 @@
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="51"/>
       <c r="B17" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" s="18">
         <v>30</v>
@@ -1341,10 +1341,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" s="15">
         <v>30</v>
@@ -1356,7 +1356,7 @@
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="50"/>
       <c r="B19" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>7</v>
@@ -1371,10 +1371,10 @@
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="A20" s="50"/>
       <c r="B20" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="17">
         <v>30</v>
@@ -1386,10 +1386,10 @@
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="50"/>
       <c r="B21" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
@@ -1401,10 +1401,10 @@
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="51"/>
       <c r="B22" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" s="18">
         <v>15</v>
@@ -1418,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
@@ -1433,7 +1433,7 @@
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="50"/>
       <c r="B24" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>10</v>
@@ -1448,7 +1448,7 @@
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="51"/>
       <c r="B25" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>11</v>
@@ -1462,15 +1462,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="A18:A22"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991B9B04-AB71-4EF7-9DB4-78C734AE5A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C885E378-500C-48E5-B670-5BCA0829940B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -110,9 +110,6 @@
     <t>Number of varieties released</t>
   </si>
   <si>
-    <t>Percentage of annual rate of genetic gain, by crop</t>
-  </si>
-  <si>
     <t>Crop Trust performance compliance rate (%)</t>
   </si>
   <si>
@@ -198,6 +195,9 @@
   </si>
   <si>
     <t>Percentage of national scientists who attended training courses who are female</t>
+  </si>
+  <si>
+    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -690,6 +690,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -706,18 +718,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1068,13 +1068,13 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>50</v>
-      </c>
       <c r="C1" s="34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D1" s="35" t="s">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1116,7 +1116,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
+      <c r="A3" s="54"/>
       <c r="B3" s="23" t="s">
         <v>15</v>
       </c>
@@ -1131,7 +1131,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
+      <c r="A4" s="55"/>
       <c r="B4" s="24" t="s">
         <v>14</v>
       </c>
@@ -1146,14 +1146,14 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="49" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="15">
         <v>150</v>
@@ -1163,10 +1163,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="50"/>
       <c r="C6" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="27">
         <v>0.5</v>
@@ -1176,12 +1176,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="57"/>
+      <c r="B7" s="51" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="19">
         <v>60</v>
@@ -1191,10 +1191,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="51"/>
       <c r="C8" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="27">
         <v>0.5</v>
@@ -1204,8 +1204,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57" t="s">
+      <c r="A9" s="57"/>
+      <c r="B9" s="51" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1219,10 +1219,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="27">
         <v>0.5</v>
@@ -1232,12 +1232,12 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="57" t="s">
+      <c r="A11" s="57"/>
+      <c r="B11" s="51" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="20">
         <v>150</v>
@@ -1247,10 +1247,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="58"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="52"/>
       <c r="C12" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="32">
         <v>0.5</v>
@@ -1260,11 +1260,11 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="53" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>22</v>
@@ -1277,12 +1277,12 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D14" s="9">
         <v>1.4999999999999999E-2</v>
@@ -1292,12 +1292,12 @@
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
@@ -1307,9 +1307,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>5</v>
@@ -1322,12 +1322,12 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
+      <c r="A17" s="55"/>
       <c r="B17" s="24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="18">
         <v>30</v>
@@ -1337,14 +1337,14 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="15">
         <v>30</v>
@@ -1354,9 +1354,9 @@
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>7</v>
@@ -1369,12 +1369,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="17">
         <v>30</v>
@@ -1384,12 +1384,12 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
@@ -1399,12 +1399,12 @@
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
+      <c r="A22" s="55"/>
       <c r="B22" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="18">
         <v>15</v>
@@ -1414,11 +1414,11 @@
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="53" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
@@ -1431,9 +1431,9 @@
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+      <c r="A24" s="54"/>
       <c r="B24" s="23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>10</v>
@@ -1446,9 +1446,9 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>11</v>
@@ -1462,15 +1462,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C885E378-500C-48E5-B670-5BCA0829940B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1073AD3-E67B-4135-BCDE-D16E7DD3A92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
   </bookViews>
@@ -690,6 +690,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -700,24 +718,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1099,7 +1099,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="49" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -1116,7 +1116,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54"/>
+      <c r="A3" s="50"/>
       <c r="B3" s="23" t="s">
         <v>15</v>
       </c>
@@ -1131,7 +1131,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="55"/>
+      <c r="A4" s="51"/>
       <c r="B4" s="24" t="s">
         <v>14</v>
       </c>
@@ -1146,10 +1146,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="55" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1163,8 +1163,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="50"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="26" t="s">
         <v>44</v>
       </c>
@@ -1176,8 +1176,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="51" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="57" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1191,8 +1191,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="51"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="29" t="s">
         <v>42</v>
       </c>
@@ -1204,8 +1204,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57"/>
-      <c r="B9" s="51" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="57" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1219,8 +1219,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="57"/>
-      <c r="B10" s="51"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="29" t="s">
         <v>50</v>
       </c>
@@ -1232,8 +1232,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="57"/>
-      <c r="B11" s="51" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="57" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1247,8 +1247,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="58"/>
-      <c r="B12" s="52"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="31" t="s">
         <v>51</v>
       </c>
@@ -1260,7 +1260,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="49" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="25" t="s">
@@ -1277,7 +1277,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="54"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="23" t="s">
         <v>30</v>
       </c>
@@ -1288,11 +1288,11 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E14" s="41">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="54"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="23" t="s">
         <v>31</v>
       </c>
@@ -1307,7 +1307,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="23" t="s">
         <v>32</v>
       </c>
@@ -1322,7 +1322,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="24" t="s">
         <v>33</v>
       </c>
@@ -1337,7 +1337,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="49" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="22" t="s">
@@ -1354,7 +1354,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="23" t="s">
         <v>35</v>
       </c>
@@ -1369,7 +1369,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="54"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="23" t="s">
         <v>36</v>
       </c>
@@ -1384,7 +1384,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="54"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="23" t="s">
         <v>37</v>
       </c>
@@ -1399,7 +1399,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="55"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="24" t="s">
         <v>38</v>
       </c>
@@ -1414,7 +1414,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="49" t="s">
         <v>8</v>
       </c>
       <c r="B23" s="22" t="s">
@@ -1431,7 +1431,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="54"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="23" t="s">
         <v>40</v>
       </c>
@@ -1446,7 +1446,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="55"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="24" t="s">
         <v>41</v>
       </c>
@@ -1462,6 +1462,7 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A12"/>
     <mergeCell ref="A13:A17"/>
@@ -1470,7 +1471,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A23:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/Program Output KPIs.xlsx
+++ b/data/Program Output KPIs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1073AD3-E67B-4135-BCDE-D16E7DD3A92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EC2D86-AAF3-401F-97D7-02E08F395EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7D6C42FC-A6F5-4FB3-BCAA-02C3B0CCB318}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,186 +18,170 @@
   <definedNames>
     <definedName name="_Hlk200085589" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
+    <t>Key Performance Indicator (KPI) Pillar</t>
+  </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>KPI Metric</t>
+  </si>
+  <si>
     <t>Annual Target</t>
   </si>
   <si>
     <t>Research Outputs</t>
   </si>
   <si>
+    <t>KPI 1</t>
+  </si>
+  <si>
     <t>Number of papers published in Thomson-indexed journals</t>
   </si>
   <si>
+    <t>KPI 2</t>
+  </si>
+  <si>
+    <t>Number of papers published in Thomson-indexed journals per Internationally Recruited Staff (IRS)</t>
+  </si>
+  <si>
+    <t>KPI 3</t>
+  </si>
+  <si>
+    <t>Number of Thomson-indexed papers published with an impact factor greater than 10</t>
+  </si>
+  <si>
     <t>Training and Capacity Building</t>
   </si>
   <si>
+    <t>KPI 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of PhD and MSc students enrolled </t>
+  </si>
+  <si>
+    <t>Percentage of PhD and MSc  students enrolled who are female</t>
+  </si>
+  <si>
+    <t>KPI 5</t>
+  </si>
+  <si>
+    <t>Number of PhD and MSc thesis accepted</t>
+  </si>
+  <si>
+    <t>Percentage of PhD and MSc  theses accepted that are by female students</t>
+  </si>
+  <si>
+    <t>KPI 6</t>
+  </si>
+  <si>
+    <t>Number of delivery partners trained</t>
+  </si>
+  <si>
+    <t>Percentage of delivery partners trained who are female</t>
+  </si>
+  <si>
+    <t>KPI 7</t>
+  </si>
+  <si>
+    <t>Number of national scientists who attended training courses</t>
+  </si>
+  <si>
+    <t>Percentage of national scientists who attended training courses who are female</t>
+  </si>
+  <si>
     <t>Product Development</t>
   </si>
   <si>
+    <t>KPI 8</t>
+  </si>
+  <si>
+    <t>Number of varieties released</t>
+  </si>
+  <si>
+    <t>KPI 9</t>
+  </si>
+  <si>
+    <t>Average (across crops) percentage yield-related genetic gain</t>
+  </si>
+  <si>
+    <t>KPI 10</t>
+  </si>
+  <si>
+    <t>Crop Trust performance compliance rate (%)</t>
+  </si>
+  <si>
+    <t>KPI 11</t>
+  </si>
+  <si>
     <t>Number of IITA innovations incorporated into the TAAT e-Catalogue</t>
   </si>
   <si>
+    <t>KPI 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of IITA innovations taken on by scaling partners </t>
+  </si>
+  <si>
     <t>Recognition and Reputation</t>
   </si>
   <si>
+    <t>KPI 13</t>
+  </si>
+  <si>
+    <t>Number of collaborations with Advanced Research Institutes (ARIs)</t>
+  </si>
+  <si>
+    <t>KPI 14</t>
+  </si>
+  <si>
     <t>Number of active collaborations with scaling partners</t>
   </si>
   <si>
+    <t>KPI 15</t>
+  </si>
+  <si>
+    <t>Number of awards to IITA staff or project teams</t>
+  </si>
+  <si>
+    <t>KPI 16</t>
+  </si>
+  <si>
+    <t>Number of invitations for presentations or seminars</t>
+  </si>
+  <si>
+    <t>KPI 17</t>
+  </si>
+  <si>
+    <t>Number of direct engagements  with senior policy makers</t>
+  </si>
+  <si>
     <t>Society Impact and Inclusion</t>
   </si>
   <si>
+    <t>KPI 18</t>
+  </si>
+  <si>
     <t>Percentage of approved proposals with gender/youth/social inclusion components</t>
   </si>
   <si>
+    <t>KPI 19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Percentage of approved proposals with inclusion of adaptation/ mitigation activities </t>
   </si>
   <si>
+    <t>KPI 20</t>
+  </si>
+  <si>
     <t>Percentage of approved proposals with inclusion of nutrition and health activities</t>
-  </si>
-  <si>
-    <t>Number of papers published in Thomson-indexed journals per Internationally Recruited Staff (IRS)</t>
-  </si>
-  <si>
-    <t>KPI 1</t>
-  </si>
-  <si>
-    <t>KPI 3</t>
-  </si>
-  <si>
-    <t>KPI 2</t>
-  </si>
-  <si>
-    <t>KPI 4</t>
-  </si>
-  <si>
-    <t>Number of Thomson-indexed papers published with an impact factor greater than 10</t>
-  </si>
-  <si>
-    <t>KPI 5</t>
-  </si>
-  <si>
-    <t>KPI 6</t>
-  </si>
-  <si>
-    <t>KPI 7</t>
-  </si>
-  <si>
-    <t>Number of delivery partners trained</t>
-  </si>
-  <si>
-    <t>Number of varieties released</t>
-  </si>
-  <si>
-    <t>Crop Trust performance compliance rate (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of IITA innovations taken on by scaling partners </t>
-  </si>
-  <si>
-    <t>Number of collaborations with Advanced Research Institutes (ARIs)</t>
-  </si>
-  <si>
-    <t>Number of awards to IITA staff or project teams</t>
-  </si>
-  <si>
-    <t>KPI 8</t>
-  </si>
-  <si>
-    <t>Number of invitations for presentations or seminars</t>
-  </si>
-  <si>
-    <t>Number of direct engagements  with senior policy makers</t>
-  </si>
-  <si>
-    <t>KPI 9</t>
-  </si>
-  <si>
-    <t>KPI 10</t>
-  </si>
-  <si>
-    <t>KPI 11</t>
-  </si>
-  <si>
-    <t>KPI 12</t>
-  </si>
-  <si>
-    <t>KPI 13</t>
-  </si>
-  <si>
-    <t>KPI 14</t>
-  </si>
-  <si>
-    <t>KPI 15</t>
-  </si>
-  <si>
-    <t>KPI 16</t>
-  </si>
-  <si>
-    <t>KPI 17</t>
-  </si>
-  <si>
-    <t>KPI 18</t>
-  </si>
-  <si>
-    <t>KPI 19</t>
-  </si>
-  <si>
-    <t>KPI 20</t>
-  </si>
-  <si>
-    <t>Percentage of PhD and MSc  theses accepted that are by female students</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of PhD and MSc students enrolled </t>
-  </si>
-  <si>
-    <t>Percentage of PhD and MSc  students enrolled who are female</t>
-  </si>
-  <si>
-    <t>Number of PhD and MSc thesis accepted</t>
-  </si>
-  <si>
-    <t>Number of national scientists who attended training courses</t>
-  </si>
-  <si>
-    <t>KPI Metric</t>
-  </si>
-  <si>
-    <t>Key Performance Indicator (KPI) Pillar</t>
-  </si>
-  <si>
-    <t>KPI</t>
-  </si>
-  <si>
-    <t>Percentage of delivery partners trained who are female</t>
-  </si>
-  <si>
-    <t>Percentage of national scientists who attended training courses who are female</t>
-  </si>
-  <si>
-    <t>Average (across crops) percentage yield-related genetic gain</t>
   </si>
 </sst>
 </file>
@@ -205,10 +189,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -273,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -417,17 +401,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -540,13 +513,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -570,7 +569,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -588,136 +587,115 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1055,425 +1033,425 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436DF3B9-9B26-4648-BD64-23BB8D8864D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="10" style="8" customWidth="1"/>
+    <col min="3" max="3" width="20" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="35" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="47">
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="45">
         <v>2025</v>
       </c>
-      <c r="F1" s="48">
+      <c r="F1" s="46">
         <v>2026</v>
       </c>
-      <c r="G1" s="48">
+      <c r="G1" s="46">
         <v>2027</v>
       </c>
-      <c r="H1" s="48">
+      <c r="H1" s="46">
         <v>2028</v>
       </c>
-      <c r="I1" s="48">
+      <c r="I1" s="46">
         <v>2029</v>
       </c>
-      <c r="J1" s="48">
+      <c r="J1" s="46">
         <v>2030</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>13</v>
+      <c r="A2" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2" s="15">
         <v>272</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="35">
         <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="23" t="s">
-        <v>15</v>
+      <c r="A3" s="48"/>
+      <c r="B3" s="22" t="s">
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="46">
+        <v>8</v>
+      </c>
+      <c r="D3" s="44">
         <v>2</v>
       </c>
-      <c r="E3" s="46">
-        <v>1.7</v>
+      <c r="E3" s="44">
+        <v>1.5</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
-      <c r="B4" s="24" t="s">
-        <v>14</v>
+      <c r="A4" s="49"/>
+      <c r="B4" s="23" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D4" s="18">
         <v>13</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="36">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="26.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D5" s="15">
         <v>150</v>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="37">
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="53"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="27">
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="48"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="26">
         <v>0.5</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <v>0.59</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53"/>
-      <c r="B7" s="57" t="s">
-        <v>18</v>
+      <c r="A7" s="48"/>
+      <c r="B7" s="50" t="s">
+        <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D7" s="19">
         <v>60</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="38">
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A8" s="53"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="27">
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="48"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="26">
         <v>0.5</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>0.49</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="57" t="s">
+      <c r="A9" s="48"/>
+      <c r="B9" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="19">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="38">
+        <v>12612</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="48"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="29">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="48"/>
+      <c r="B11" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="20">
-        <v>12000</v>
-      </c>
-      <c r="E9" s="39">
-        <v>12612</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="27">
+      <c r="C11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="19">
+        <v>150</v>
+      </c>
+      <c r="E11" s="38">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="49"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="31">
         <v>0.5</v>
       </c>
-      <c r="E10" s="30">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53"/>
-      <c r="B11" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="20">
-        <v>150</v>
-      </c>
-      <c r="E11" s="39">
-        <v>1444</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="33">
+      <c r="E12" s="32">
         <v>0.34</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>27</v>
+      <c r="A13" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D13" s="16">
         <v>6</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="35">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="50"/>
-      <c r="B14" s="23" t="s">
-        <v>30</v>
+      <c r="A14" s="48"/>
+      <c r="B14" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D14" s="9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="39">
         <v>1.2E-2</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
-      <c r="B15" s="23" t="s">
-        <v>31</v>
+      <c r="A15" s="48"/>
+      <c r="B15" s="22" t="s">
+        <v>29</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D15" s="10">
         <v>1</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="40">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-      <c r="B16" s="23" t="s">
+      <c r="A16" s="48"/>
+      <c r="B16" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>5</v>
       </c>
       <c r="D16" s="17">
         <v>20</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="41">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="51"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="49"/>
+      <c r="B17" s="23" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D17" s="18">
         <v>30</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="36">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>34</v>
+      <c r="A18" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D18" s="15">
         <v>30</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="35">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="23" t="s">
-        <v>35</v>
+      <c r="A19" s="48"/>
+      <c r="B19" s="22" t="s">
+        <v>38</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D19" s="17">
         <v>25</v>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="41">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
-      <c r="B20" s="23" t="s">
-        <v>36</v>
+    <row r="20" spans="1:5" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="48"/>
+      <c r="B20" s="22" t="s">
+        <v>40</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D20" s="17">
         <v>30</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="41">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
-      <c r="B21" s="23" t="s">
-        <v>37</v>
+    <row r="21" spans="1:5" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="48"/>
+      <c r="B21" s="22" t="s">
+        <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="41">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="24" t="s">
-        <v>38</v>
+    <row r="22" spans="1:5" s="2" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="49"/>
+      <c r="B22" s="23" t="s">
+        <v>44</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D22" s="18">
         <v>15</v>
       </c>
-      <c r="E22" s="37">
+      <c r="E22" s="36">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>39</v>
+      <c r="A23" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>47</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D23" s="11">
         <v>0.25</v>
       </c>
-      <c r="E23" s="44">
+      <c r="E23" s="42">
         <v>0.41660000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:5" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="23" t="s">
-        <v>40</v>
+    <row r="24" spans="1:5" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="48"/>
+      <c r="B24" s="22" t="s">
+        <v>49</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D24" s="12">
         <v>0.25</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="40">
         <v>0.36</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51"/>
-      <c r="B25" s="24" t="s">
-        <v>41</v>
+    <row r="25" spans="1:5" s="2" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="49"/>
+      <c r="B25" s="23" t="s">
+        <v>51</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D25" s="13">
         <v>0.25</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="43">
         <v>0.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="B9:B10"/>
     <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="A5:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
